--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2016_T4_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2016_T4_0.xlsx
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>90</t>
+    <t>86</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -57,40 +57,40 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>0.200</t>
-  </si>
-  <si>
-    <t>(0.042)</t>
-  </si>
-  <si>
-    <t>0.344</t>
-  </si>
-  <si>
-    <t>(0.050)</t>
-  </si>
-  <si>
-    <t>0.100</t>
-  </si>
-  <si>
-    <t>(0.032)</t>
-  </si>
-  <si>
-    <t>0.422</t>
-  </si>
-  <si>
-    <t>(0.142)</t>
-  </si>
-  <si>
-    <t>0.644</t>
-  </si>
-  <si>
-    <t>(0.122)</t>
-  </si>
-  <si>
-    <t>0.122</t>
-  </si>
-  <si>
-    <t>(0.041)</t>
+    <t>0.209</t>
+  </si>
+  <si>
+    <t>(0.044)</t>
+  </si>
+  <si>
+    <t>0.360</t>
+  </si>
+  <si>
+    <t>(0.052)</t>
+  </si>
+  <si>
+    <t>0.105</t>
+  </si>
+  <si>
+    <t>(0.033)</t>
+  </si>
+  <si>
+    <t>0.442</t>
+  </si>
+  <si>
+    <t>(0.149)</t>
+  </si>
+  <si>
+    <t>0.674</t>
+  </si>
+  <si>
+    <t>(0.126)</t>
+  </si>
+  <si>
+    <t>0.128</t>
+  </si>
+  <si>
+    <t>(0.043)</t>
   </si>
   <si>
     <t>24</t>
@@ -135,7 +135,7 @@
     <t>(0.119)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -147,22 +147,22 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.217**</t>
-  </si>
-  <si>
-    <t>0.447***</t>
-  </si>
-  <si>
-    <t>0.275***</t>
-  </si>
-  <si>
-    <t>0.494</t>
-  </si>
-  <si>
-    <t>1.647***</t>
-  </si>
-  <si>
-    <t>0.294***</t>
+    <t>0.207**</t>
+  </si>
+  <si>
+    <t>0.431***</t>
+  </si>
+  <si>
+    <t>0.270***</t>
+  </si>
+  <si>
+    <t>0.475</t>
+  </si>
+  <si>
+    <t>1.617***</t>
+  </si>
+  <si>
+    <t>0.289***</t>
   </si>
 </sst>
 </file>
